--- a/PS-VRP/dist/Schedulatore/Dati_output/schedulazione.xlsx
+++ b/PS-VRP/dist/Schedulatore/Dati_output/schedulazione.xlsx
@@ -625,7 +625,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>255338</v>
+        <v>254460</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -634,14 +634,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30-11-2025 14:00:00</t>
+          <t>21-10-2025 14:00:00</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" t="n">
-        <v>396.825</v>
+        <v>46.68333333333333</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -650,21 +650,21 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>02-12-2025 08:54:23</t>
+          <t>02-12-2025 08:56:23</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>02-12-2025 08:54:23</t>
+          <t>02-12-2025 08:56:23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>03-12-2025 07:31:12</t>
+          <t>02-12-2025 09:43:04</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>47619</v>
+        <v>5602</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -677,14 +677,11 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>70</v>
       </c>
-      <c r="O3" t="n">
-        <v>40745</v>
-      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
@@ -693,19 +690,19 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>16-12-2025 00:00:00</t>
+          <t>23-10-2025 00:00:00</t>
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>0</v>
+        <v>-50.40490740740741</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>254897</v>
+        <v>254948</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -714,37 +711,37 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>30.96666666666667</v>
+        <v>79.40833333333333</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03-12-2025 07:31:12</t>
+          <t>02-12-2025 09:43:04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>03-12-2025 07:50:12</t>
+          <t>02-12-2025 10:00:04</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>03-12-2025 07:50:12</t>
+          <t>02-12-2025 10:00:04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>03-12-2025 08:21:10</t>
+          <t>02-12-2025 11:19:28</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3716</v>
+        <v>9529</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -757,13 +754,13 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>70</v>
       </c>
       <c r="O4" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -771,23 +768,23 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S4" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>254569</v>
+        <v>255170</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -796,37 +793,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>39.75833333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>03-12-2025 08:21:10</t>
+          <t>02-12-2025 11:19:28</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:10</t>
+          <t>02-12-2025 11:53:28</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:10</t>
+          <t>02-12-2025 11:53:28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>03-12-2025 09:17:56</t>
+          <t>02-12-2025 12:01:48</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>4771</v>
+        <v>1000</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -835,17 +832,17 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>3</v>
       </c>
       <c r="N5" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O5" t="n">
-        <v>40745</v>
+        <v>40744</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -853,11 +850,11 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>40745</v>
+        <v>40744</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>30-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S5" s="1" t="n">
@@ -869,7 +866,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>255221</v>
+        <v>254532</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -882,33 +879,33 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
-        <v>30.01666666666667</v>
+        <v>83.34166666666667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>03-12-2025 09:17:56</t>
+          <t>02-12-2025 12:01:48</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>03-12-2025 09:49:56</t>
+          <t>02-12-2025 12:18:48</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>03-12-2025 09:49:56</t>
+          <t>02-12-2025 12:18:48</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>03-12-2025 10:19:57</t>
+          <t>02-12-2025 13:42:09</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3602</v>
+        <v>10001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -921,7 +918,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
         <v>76</v>
@@ -939,19 +936,19 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S6" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>254739</v>
+        <v>254531</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -964,33 +961,33 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E7" t="n">
-        <v>92.65833333333333</v>
+        <v>44.15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03-12-2025 10:19:57</t>
+          <t>02-12-2025 13:42:09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>03-12-2025 10:36:57</t>
+          <t>02-12-2025 13:57:09</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>03-12-2025 10:36:57</t>
+          <t>02-12-2025 13:57:09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>03-12-2025 12:09:36</t>
+          <t>02-12-2025 14:41:18</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>11119</v>
+        <v>5298</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -999,39 +996,41 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N7" t="n">
         <v>76</v>
       </c>
       <c r="O7" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>15-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>254736</v>
+        <v>254573</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1040,37 +1039,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>150.45</v>
+        <v>46.39166666666667</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>03-12-2025 12:09:36</t>
+          <t>02-12-2025 14:41:18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>03-12-2025 12:24:36</t>
+          <t>03-12-2025 07:13:18</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>03-12-2025 12:24:36</t>
+          <t>03-12-2025 07:13:18</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>03-12-2025 14:55:03</t>
+          <t>03-12-2025 07:59:41</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18054</v>
+        <v>5567</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1079,31 +1078,33 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>3</v>
       </c>
       <c r="N8" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O8" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>09-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -1111,7 +1112,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>254853</v>
+        <v>254895</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1120,37 +1121,37 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="E9" t="n">
-        <v>52.99166666666667</v>
+        <v>53.88333333333333</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>03-12-2025 14:55:03</t>
+          <t>03-12-2025 07:59:41</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>04-12-2025 07:29:03</t>
+          <t>03-12-2025 08:16:41</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>04-12-2025 07:29:03</t>
+          <t>03-12-2025 08:16:41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>04-12-2025 08:22:03</t>
+          <t>03-12-2025 09:10:34</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6359</v>
+        <v>6466</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1159,23 +1160,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
         <v>70</v>
       </c>
       <c r="O9" t="n">
-        <v>40684</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1183,15 +1186,15 @@
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>254856</v>
+        <v>244023</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1200,37 +1203,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>17-09-2024 14:00:00</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E10" t="n">
-        <v>141.8416666666667</v>
+        <v>8.308333333333334</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>04-12-2025 08:22:03</t>
+          <t>03-12-2025 09:10:34</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>04-12-2025 08:39:03</t>
+          <t>03-12-2025 09:33:34</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>04-12-2025 08:39:03</t>
+          <t>03-12-2025 09:33:34</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>04-12-2025 11:00:53</t>
+          <t>03-12-2025 09:41:53</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>17021</v>
+        <v>997</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1248,9 +1251,6 @@
       <c r="N10" t="n">
         <v>70</v>
       </c>
-      <c r="O10" t="n">
-        <v>40684</v>
-      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
@@ -1259,19 +1259,19 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>30-09-2024 00:00:00</t>
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>-8</v>
+        <v>-60</v>
       </c>
       <c r="T10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>255102</v>
+        <v>254853</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1287,30 +1287,30 @@
         <v>17</v>
       </c>
       <c r="E11" t="n">
-        <v>142.55</v>
+        <v>52.99166666666667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>04-12-2025 11:00:53</t>
+          <t>03-12-2025 09:41:53</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>04-12-2025 11:17:53</t>
+          <t>03-12-2025 09:58:53</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>04-12-2025 11:17:53</t>
+          <t>03-12-2025 09:58:53</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>04-12-2025 13:40:26</t>
+          <t>03-12-2025 10:51:52</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>17106</v>
+        <v>6359</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1328,6 +1328,9 @@
       <c r="N11" t="n">
         <v>70</v>
       </c>
+      <c r="O11" t="n">
+        <v>40684</v>
+      </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
@@ -1336,11 +1339,11 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>31-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="T11" t="n">
         <v>2</v>
@@ -1348,7 +1351,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>254364</v>
+        <v>254454</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1357,37 +1360,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>25-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>26.48333333333333</v>
+        <v>49.975</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>04-12-2025 13:40:26</t>
+          <t>03-12-2025 10:51:52</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>04-12-2025 13:59:26</t>
+          <t>03-12-2025 11:12:52</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>04-12-2025 13:59:26</t>
+          <t>03-12-2025 11:12:52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>04-12-2025 14:25:55</t>
+          <t>03-12-2025 12:02:51</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3178</v>
+        <v>5997</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1400,7 +1403,7 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N12" t="n">
         <v>70</v>
@@ -1413,19 +1416,19 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>13-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>-29.59223379629629</v>
+        <v>-30.50197916666667</v>
       </c>
       <c r="T12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>254898</v>
+        <v>254379</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1434,37 +1437,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="E13" t="n">
-        <v>30.96666666666667</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>04-12-2025 14:25:55</t>
+          <t>03-12-2025 12:02:51</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>04-12-2025 14:42:55</t>
+          <t>03-12-2025 12:25:51</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>04-12-2025 14:42:55</t>
+          <t>03-12-2025 12:25:51</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>05-12-2025 07:13:53</t>
+          <t>03-12-2025 13:57:27</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3716</v>
+        <v>10992</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1482,32 +1485,27 @@
       <c r="N13" t="n">
         <v>70</v>
       </c>
-      <c r="O13" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P13" t="n">
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>-0.2922106481481481</v>
+        <v>-8.5815625</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>254585</v>
+        <v>254551</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1520,33 +1518,33 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E14" t="n">
-        <v>46.675</v>
+        <v>189.8666666666667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>05-12-2025 07:13:53</t>
+          <t>03-12-2025 13:57:27</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>05-12-2025 07:30:53</t>
+          <t>03-12-2025 14:16:27</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>05-12-2025 07:30:53</t>
+          <t>03-12-2025 14:16:27</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>05-12-2025 08:17:34</t>
+          <t>04-12-2025 09:26:19</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>5601</v>
+        <v>22784</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1555,17 +1553,17 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N14" t="n">
         <v>70</v>
       </c>
       <c r="O14" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1573,23 +1571,23 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>-0.3364293981481482</v>
+        <v>-0.393275462962963</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>254582</v>
+        <v>254915</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1598,37 +1596,37 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>30-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>46.675</v>
+        <v>48.875</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>05-12-2025 08:17:34</t>
+          <t>04-12-2025 09:26:19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>05-12-2025 08:32:34</t>
+          <t>04-12-2025 09:43:19</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>05-12-2025 08:32:34</t>
+          <t>04-12-2025 09:43:19</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>05-12-2025 09:19:14</t>
+          <t>04-12-2025 10:32:11</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>5601</v>
+        <v>5865</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1637,41 +1635,36 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N15" t="n">
         <v>70</v>
       </c>
-      <c r="O15" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P15" t="n">
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>12-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>-0.3792592592592592</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>254258</v>
+        <v>254819</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1680,37 +1673,37 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>27-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E16" t="n">
-        <v>144.675</v>
+        <v>54.54166666666666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>05-12-2025 09:19:14</t>
+          <t>04-12-2025 10:32:11</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>05-12-2025 09:36:14</t>
+          <t>04-12-2025 10:53:11</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>05-12-2025 09:36:14</t>
+          <t>04-12-2025 10:53:11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>05-12-2025 12:00:55</t>
+          <t>04-12-2025 11:47:44</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>17361</v>
+        <v>6545</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1723,7 +1716,7 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N16" t="n">
         <v>70</v>
@@ -1736,19 +1729,19 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>-10.49153356481481</v>
+        <v>-16.49148148148148</v>
       </c>
       <c r="T16" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>254881</v>
+        <v>254818</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1757,37 +1750,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>15</v>
       </c>
       <c r="E17" t="n">
-        <v>144.675</v>
+        <v>44.475</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>05-12-2025 12:00:55</t>
+          <t>04-12-2025 11:47:44</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>05-12-2025 12:15:55</t>
+          <t>04-12-2025 12:02:44</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>05-12-2025 12:15:55</t>
+          <t>04-12-2025 12:02:44</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>05-12-2025 14:40:35</t>
+          <t>04-12-2025 12:47:12</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>17361</v>
+        <v>5337</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1800,7 +1793,7 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N17" t="n">
         <v>70</v>
@@ -1813,58 +1806,58 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>-10.60241898148148</v>
+        <v>-16.53278356481481</v>
       </c>
       <c r="T17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>254708</v>
+        <v>254511</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E18" t="n">
-        <v>67.84999999999999</v>
+        <v>129.5916666666667</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>05-12-2025 14:40:35</t>
+          <t>03-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>05-12-2025 14:59:35</t>
+          <t>03-12-2025 07:29:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>05-12-2025 14:59:35</t>
+          <t>03-12-2025 07:29:00</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>08-12-2025 08:07:26</t>
+          <t>03-12-2025 09:38:35</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>8142</v>
+        <v>15551</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1873,80 +1866,75 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="N18" t="n">
-        <v>70</v>
-      </c>
-      <c r="O18" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>09-12-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>-1.329398148148148</v>
+        <v>-26.40179976851852</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>255028</v>
+        <v>254894</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="E19" t="n">
-        <v>280.55</v>
+        <v>107.7666666666667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>08-12-2025 08:07:26</t>
+          <t>03-12-2025 09:38:35</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>08-12-2025 08:22:26</t>
+          <t>03-12-2025 10:24:35</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>08-12-2025 08:22:26</t>
+          <t>03-12-2025 10:24:35</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>08-12-2025 13:02:59</t>
+          <t>03-12-2025 12:12:21</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>33666</v>
+        <v>12932</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1964,66 +1952,71 @@
       <c r="N19" t="n">
         <v>70</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
+      <c r="O19" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>08-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>-7.534641203703703</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>255233</v>
+        <v>254424</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E20" t="n">
-        <v>92.41666666666667</v>
+        <v>10.95833333333333</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>08-12-2025 13:02:59</t>
+          <t>03-12-2025 12:12:21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>08-12-2025 13:17:59</t>
+          <t>03-12-2025 12:39:21</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>08-12-2025 13:17:59</t>
+          <t>03-12-2025 12:39:21</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>08-12-2025 14:50:24</t>
+          <t>03-12-2025 12:50:19</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>11090</v>
+        <v>1315</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2032,11 +2025,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
         <v>70</v>
@@ -2049,58 +2042,58 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>-0.6092361111111111</v>
+        <v>-15.53494212962963</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>255063</v>
+        <v>254855</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>05-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>184.2833333333333</v>
+        <v>46.75833333333333</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>08-12-2025 14:50:24</t>
+          <t>03-12-2025 12:50:19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>09-12-2025 07:05:24</t>
+          <t>03-12-2025 13:17:19</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>09-12-2025 07:05:24</t>
+          <t>03-12-2025 13:17:19</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>09-12-2025 10:09:41</t>
+          <t>03-12-2025 14:04:04</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>22114</v>
+        <v>5611</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -2109,15 +2102,18 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>70</v>
       </c>
+      <c r="O21" t="n">
+        <v>40684</v>
+      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -2126,11 +2122,11 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>09-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>-9.414293981481482</v>
+        <v>-8</v>
       </c>
       <c r="T21" t="n">
         <v>2</v>
@@ -2138,46 +2134,46 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>254013</v>
+        <v>254938</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BIMEC 3</t>
+          <t>BIMEC 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E22" t="n">
-        <v>182.9916666666667</v>
+        <v>90.58333333333333</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>09-12-2025 10:09:41</t>
+          <t>03-12-2025 14:04:04</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>09-12-2025 10:26:41</t>
+          <t>03-12-2025 14:31:04</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>09-12-2025 10:26:41</t>
+          <t>03-12-2025 14:31:04</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>09-12-2025 13:29:41</t>
+          <t>04-12-2025 08:01:39</t>
         </is>
       </c>
       <c r="J22" t="n">
-        <v>21959</v>
+        <v>10870</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2186,11 +2182,11 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N22" t="n">
         <v>70</v>
@@ -2203,19 +2199,19 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>26-11-2025 00:00:00</t>
+          <t>09-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>-22.55317708333333</v>
+        <v>-5.334484953703703</v>
       </c>
       <c r="T22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>254812</v>
+        <v>254978</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2224,37 +2220,37 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>29</v>
       </c>
       <c r="E23" t="n">
-        <v>41.60833333333333</v>
+        <v>22.81666666666667</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>04-12-2025 08:01:39</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>03-12-2025 07:29:00</t>
+          <t>04-12-2025 08:30:39</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>03-12-2025 07:29:00</t>
+          <t>04-12-2025 08:30:39</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>03-12-2025 08:10:36</t>
+          <t>04-12-2025 08:53:28</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4993</v>
+        <v>2738</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2263,28 +2259,33 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M23" t="n">
         <v>3</v>
       </c>
       <c r="N23" t="n">
-        <v>76</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O23" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>25-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>-18.34070023148148</v>
+        <v>-0.37046875</v>
       </c>
       <c r="T23" t="n">
         <v>7</v>
@@ -2292,7 +2293,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>254573</v>
+        <v>254255</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2301,37 +2302,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>46.39166666666667</v>
+        <v>43.45833333333334</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>03-12-2025 08:10:36</t>
+          <t>04-12-2025 08:53:28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>03-12-2025 08:54:36</t>
+          <t>04-12-2025 09:20:28</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>03-12-2025 08:54:36</t>
+          <t>04-12-2025 09:20:28</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>03-12-2025 09:41:00</t>
+          <t>04-12-2025 10:03:56</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>5567</v>
+        <v>5215</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2344,37 +2345,32 @@
         </is>
       </c>
       <c r="M24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
         <v>70</v>
       </c>
-      <c r="O24" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P24" t="n">
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>09-12-2025 00:00:00</t>
+          <t>02-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>0</v>
+        <v>-42.41939814814815</v>
       </c>
       <c r="T24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>254895</v>
+        <v>254766</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2383,37 +2379,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E25" t="n">
-        <v>53.88333333333333</v>
+        <v>81.14166666666667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>03-12-2025 09:41:00</t>
+          <t>04-12-2025 10:03:56</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>03-12-2025 10:08:00</t>
+          <t>04-12-2025 10:34:56</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>03-12-2025 10:08:00</t>
+          <t>04-12-2025 10:34:56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>03-12-2025 11:01:53</t>
+          <t>04-12-2025 11:56:04</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>6466</v>
+        <v>9737</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2422,80 +2418,75 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>70</v>
       </c>
-      <c r="O25" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P25" t="n">
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>0</v>
+        <v>-16.49727430555556</v>
       </c>
       <c r="T25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>254645</v>
+        <v>254872</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>27-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E26" t="n">
-        <v>58.36666666666667</v>
+        <v>41.28333333333333</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>03-12-2025 11:01:53</t>
+          <t>02-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>03-12-2025 11:43:53</t>
+          <t>02-12-2025 07:17:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>03-12-2025 11:43:53</t>
+          <t>02-12-2025 07:17:00</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>03-12-2025 12:42:15</t>
+          <t>02-12-2025 07:58:17</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>7004</v>
+        <v>4954</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2513,66 +2504,71 @@
       <c r="N26" t="n">
         <v>76</v>
       </c>
-      <c r="P26" t="n">
-        <v>0</v>
+      <c r="O26" t="n">
+        <v>40744</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>40744</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>-8.529340277777777</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>254855</v>
+        <v>254736</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E27" t="n">
-        <v>46.75833333333333</v>
+        <v>150.45</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>03-12-2025 12:42:15</t>
+          <t>02-12-2025 07:58:17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>03-12-2025 13:24:15</t>
+          <t>02-12-2025 08:13:17</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>03-12-2025 13:24:15</t>
+          <t>02-12-2025 08:13:17</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>03-12-2025 14:11:00</t>
+          <t>02-12-2025 10:43:44</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>5611</v>
+        <v>18054</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2581,17 +2577,17 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O27" t="n">
-        <v>40684</v>
+        <v>40731</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
@@ -2601,58 +2597,58 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="T27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>254819</v>
+        <v>254739</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>27-11-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E28" t="n">
-        <v>54.54166666666666</v>
+        <v>92.65833333333333</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>03-12-2025 14:11:00</t>
+          <t>02-12-2025 10:43:44</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>03-12-2025 14:38:00</t>
+          <t>02-12-2025 10:58:44</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>03-12-2025 14:38:00</t>
+          <t>02-12-2025 10:58:44</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>04-12-2025 07:32:33</t>
+          <t>02-12-2025 12:31:23</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>6545</v>
+        <v>11119</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2661,14 +2657,17 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>70</v>
+        <v>76</v>
+      </c>
+      <c r="O28" t="n">
+        <v>40731</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2682,54 +2681,54 @@
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>-16.31427083333333</v>
+        <v>-6</v>
       </c>
       <c r="T28" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>254818</v>
+        <v>251289</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>44.475</v>
+        <v>161.0333333333333</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>04-12-2025 07:32:33</t>
+          <t>02-12-2025 12:31:23</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>04-12-2025 07:57:33</t>
+          <t>02-12-2025 13:03:23</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>04-12-2025 07:57:33</t>
+          <t>02-12-2025 13:03:23</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>04-12-2025 08:42:01</t>
+          <t>03-12-2025 07:44:25</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>5337</v>
+        <v>19324</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2742,11 +2741,14 @@
         </is>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
         <v>70</v>
       </c>
+      <c r="O29" t="n">
+        <v>40731</v>
+      </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
@@ -2755,58 +2757,58 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>-16.36251736111111</v>
+        <v>-3</v>
       </c>
       <c r="T29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>254766</v>
+        <v>254592</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E30" t="n">
-        <v>81.14166666666667</v>
+        <v>59.86666666666667</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>04-12-2025 08:42:01</t>
+          <t>03-12-2025 07:44:25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>04-12-2025 09:09:01</t>
+          <t>03-12-2025 08:03:25</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>04-12-2025 09:09:01</t>
+          <t>03-12-2025 08:03:25</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>04-12-2025 10:30:10</t>
+          <t>03-12-2025 09:03:17</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>9737</v>
+        <v>7184</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2815,75 +2817,80 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N30" t="n">
         <v>70</v>
       </c>
-      <c r="P30" t="n">
-        <v>0</v>
+      <c r="O30" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>-16.43761574074074</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>254496</v>
+        <v>254590</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BIMEC 4</t>
+          <t>BIMEC 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E31" t="n">
-        <v>53.50833333333333</v>
+        <v>46.675</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>04-12-2025 10:30:10</t>
+          <t>03-12-2025 09:03:17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>04-12-2025 10:57:10</t>
+          <t>03-12-2025 09:20:17</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>04-12-2025 10:57:10</t>
+          <t>03-12-2025 09:20:17</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>04-12-2025 11:50:40</t>
+          <t>03-12-2025 10:06:58</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>6421</v>
+        <v>5601</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2896,32 +2903,37 @@
         </is>
       </c>
       <c r="M31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N31" t="n">
         <v>70</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
+      <c r="O31" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>-30.49352430555556</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>255334</v>
+        <v>254569</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -2930,37 +2942,37 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32" t="n">
-        <v>153.9583333333333</v>
+        <v>39.75833333333333</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>02-12-2025 07:00:00</t>
+          <t>03-12-2025 10:06:58</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>02-12-2025 07:17:00</t>
+          <t>03-12-2025 10:21:58</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>02-12-2025 07:17:00</t>
+          <t>03-12-2025 10:21:58</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>02-12-2025 09:50:57</t>
+          <t>03-12-2025 11:01:43</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>18475</v>
+        <v>4771</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2969,27 +2981,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
       <c r="N32" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O32" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>07-01-2026 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S32" s="1" t="n">
@@ -3001,7 +3015,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>254872</v>
+        <v>254897</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3010,37 +3024,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>27-11-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>41.28333333333333</v>
+        <v>30.96666666666667</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>02-12-2025 09:50:57</t>
+          <t>03-12-2025 11:01:43</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>02-12-2025 10:05:57</t>
+          <t>03-12-2025 11:18:43</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>02-12-2025 10:05:57</t>
+          <t>03-12-2025 11:18:43</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>02-12-2025 10:47:14</t>
+          <t>03-12-2025 11:49:41</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>4954</v>
+        <v>3716</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -3049,17 +3063,17 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N33" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O33" t="n">
-        <v>40744</v>
+        <v>40745</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3067,7 +3081,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>40744</v>
+        <v>40745</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3083,7 +3097,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>254537</v>
+        <v>235572</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3092,37 +3106,37 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>30-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>17</v>
       </c>
       <c r="E34" t="n">
-        <v>41.63333333333333</v>
+        <v>82.98333333333333</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>02-12-2025 10:47:14</t>
+          <t>03-12-2025 11:49:41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>02-12-2025 11:04:14</t>
+          <t>03-12-2025 12:06:41</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>02-12-2025 11:04:14</t>
+          <t>03-12-2025 12:06:41</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>02-12-2025 11:45:52</t>
+          <t>03-12-2025 13:29:40</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>4996</v>
+        <v>9958</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -3131,41 +3145,39 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N34" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O34" t="n">
         <v>40745</v>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P34" t="n">
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>06-11-2023 00:00:00</t>
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="T34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>254540</v>
+        <v>254359</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3174,37 +3186,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>15</v>
       </c>
       <c r="E35" t="n">
-        <v>41.63333333333333</v>
+        <v>23.19166666666667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>02-12-2025 11:45:52</t>
+          <t>03-12-2025 13:29:40</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>02-12-2025 12:00:52</t>
+          <t>03-12-2025 13:44:40</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>02-12-2025 12:00:52</t>
+          <t>03-12-2025 13:44:40</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>02-12-2025 12:42:30</t>
+          <t>03-12-2025 14:07:52</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>4996</v>
+        <v>2783</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3213,41 +3225,39 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N35" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O35" t="n">
         <v>40745</v>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P35" t="n">
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>254948</v>
+        <v>254700</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3256,37 +3266,37 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>27-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>79.40833333333333</v>
+        <v>91.72499999999999</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>02-12-2025 12:42:30</t>
+          <t>03-12-2025 14:07:52</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>02-12-2025 13:14:30</t>
+          <t>03-12-2025 14:26:52</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>02-12-2025 13:14:30</t>
+          <t>03-12-2025 14:26:52</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>02-12-2025 14:33:55</t>
+          <t>04-12-2025 07:58:35</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>9529</v>
+        <v>11007</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3304,32 +3314,27 @@
       <c r="N36" t="n">
         <v>70</v>
       </c>
-      <c r="O36" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P36" t="n">
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>40731</v>
+        <v>0</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>19-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S36" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>254894</v>
+        <v>254645</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3338,37 +3343,37 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E37" t="n">
-        <v>107.7666666666667</v>
+        <v>58.36666666666667</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>02-12-2025 14:33:55</t>
+          <t>04-12-2025 07:58:35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>02-12-2025 14:50:55</t>
+          <t>04-12-2025 08:32:35</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>02-12-2025 14:50:55</t>
+          <t>04-12-2025 08:32:35</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:41</t>
+          <t>04-12-2025 09:30:57</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>12932</v>
+        <v>7004</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -3377,41 +3382,36 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N37" t="n">
-        <v>70</v>
-      </c>
-      <c r="O37" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>04-12-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>0</v>
+        <v>-8.53962962962963</v>
       </c>
       <c r="T37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>254590</v>
+        <v>254824</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3420,37 +3420,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>30-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D38" t="n">
         <v>17</v>
       </c>
       <c r="E38" t="n">
-        <v>46.675</v>
+        <v>748.225</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>03-12-2025 08:38:41</t>
+          <t>04-12-2025 09:30:57</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>03-12-2025 08:55:41</t>
+          <t>04-12-2025 09:47:57</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>03-12-2025 08:55:41</t>
+          <t>04-12-2025 09:47:57</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>03-12-2025 09:42:21</t>
+          <t>05-12-2025 14:16:11</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>5601</v>
+        <v>89787</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3459,41 +3459,36 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>70</v>
-      </c>
-      <c r="O38" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>16-03-2026 00:00:00</t>
         </is>
       </c>
       <c r="S38" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>235572</v>
+        <v>254535</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3502,37 +3497,37 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>30-11-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>19</v>
       </c>
       <c r="E39" t="n">
-        <v>82.98333333333333</v>
+        <v>26.04166666666667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>03-12-2025 09:42:21</t>
+          <t>05-12-2025 14:16:11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>03-12-2025 10:01:21</t>
+          <t>05-12-2025 14:35:11</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>03-12-2025 10:01:21</t>
+          <t>05-12-2025 14:35:11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>03-12-2025 11:24:20</t>
+          <t>08-12-2025 07:01:13</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>9958</v>
+        <v>3125</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3541,17 +3536,14 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39" t="n">
-        <v>70</v>
-      </c>
-      <c r="O39" t="n">
-        <v>40745</v>
+        <v>76</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -3561,19 +3553,19 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>06-11-2023 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>-60</v>
+        <v>-31.43564814814815</v>
       </c>
       <c r="T39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>254359</v>
+        <v>254654</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3582,37 +3574,37 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E40" t="n">
-        <v>23.19166666666667</v>
+        <v>80.51666666666667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>03-12-2025 11:24:20</t>
+          <t>08-12-2025 07:01:13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>03-12-2025 11:39:20</t>
+          <t>08-12-2025 07:37:13</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>03-12-2025 11:39:20</t>
+          <t>08-12-2025 07:37:13</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>03-12-2025 12:02:32</t>
+          <t>08-12-2025 08:57:44</t>
         </is>
       </c>
       <c r="J40" t="n">
-        <v>2783</v>
+        <v>9662</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3625,14 +3617,11 @@
         </is>
       </c>
       <c r="M40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
         <v>70</v>
       </c>
-      <c r="O40" t="n">
-        <v>40745</v>
-      </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
@@ -3641,19 +3630,19 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>-20</v>
+        <v>-24.5165625</v>
       </c>
       <c r="T40" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>254460</v>
+        <v>254013</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -3662,37 +3651,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21-10-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E41" t="n">
-        <v>46.68333333333333</v>
+        <v>182.9916666666667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>03-12-2025 12:02:32</t>
+          <t>08-12-2025 08:57:44</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>03-12-2025 12:19:32</t>
+          <t>08-12-2025 09:16:44</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>03-12-2025 12:19:32</t>
+          <t>08-12-2025 09:16:44</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>03-12-2025 13:06:13</t>
+          <t>08-12-2025 12:19:44</t>
         </is>
       </c>
       <c r="J41" t="n">
-        <v>5602</v>
+        <v>21959</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3701,11 +3690,11 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N41" t="n">
         <v>70</v>
@@ -3718,19 +3707,19 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>23-10-2025 00:00:00</t>
+          <t>26-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>-51.43122106481481</v>
+        <v>-22.32350115740741</v>
       </c>
       <c r="T41" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>254379</v>
+        <v>254269</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -3739,37 +3728,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>05-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E42" t="n">
-        <v>91.59999999999999</v>
+        <v>47.275</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>03-12-2025 13:06:13</t>
+          <t>08-12-2025 12:19:44</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>03-12-2025 13:27:13</t>
+          <t>08-12-2025 12:38:44</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>03-12-2025 13:27:13</t>
+          <t>08-12-2025 12:38:44</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>03-12-2025 14:58:49</t>
+          <t>08-12-2025 13:26:00</t>
         </is>
       </c>
       <c r="J42" t="n">
-        <v>10992</v>
+        <v>5673</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3795,19 +3784,19 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>06-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>-8.509415509259259</v>
+        <v>-12.36952546296296</v>
       </c>
       <c r="T42" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>254820</v>
+        <v>255084</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -3816,37 +3805,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>05-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E43" t="n">
-        <v>57.46666666666667</v>
+        <v>47.65</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>03-12-2025 14:58:49</t>
+          <t>08-12-2025 13:26:00</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>04-12-2025 07:19:49</t>
+          <t>08-12-2025 13:43:00</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>04-12-2025 07:19:49</t>
+          <t>08-12-2025 13:43:00</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>04-12-2025 08:17:17</t>
+          <t>08-12-2025 14:30:39</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>6896</v>
+        <v>5718</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3859,7 +3848,7 @@
         </is>
       </c>
       <c r="M43" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N43" t="n">
         <v>70</v>
@@ -3872,19 +3861,19 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>10-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>-16.57814236111111</v>
+        <v>-8.414421296296297</v>
       </c>
       <c r="T43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>254454</v>
+        <v>254167</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -3893,37 +3882,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>25-11-2025 14:00:00</t>
+          <t>05-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E44" t="n">
-        <v>49.975</v>
+        <v>152.125</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>04-12-2025 08:17:17</t>
+          <t>08-12-2025 14:30:39</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>04-12-2025 08:40:17</t>
+          <t>08-12-2025 14:49:39</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>04-12-2025 08:40:17</t>
+          <t>08-12-2025 14:49:39</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>04-12-2025 09:30:15</t>
+          <t>09-12-2025 09:21:47</t>
         </is>
       </c>
       <c r="J44" t="n">
-        <v>5997</v>
+        <v>18255</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3936,7 +3925,7 @@
         </is>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
         <v>70</v>
@@ -3949,58 +3938,58 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>13-11-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>-30.56009259259259</v>
+        <v>-16.53325810185185</v>
       </c>
       <c r="T44" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>254824</v>
+        <v>254866</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>30-11-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>42</v>
+        <v>32.5</v>
       </c>
       <c r="E45" t="n">
-        <v>748.225</v>
+        <v>120.875</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>04-12-2025 09:30:15</t>
+          <t>02-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>04-12-2025 10:12:15</t>
+          <t>02-12-2025 07:32:30</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>04-12-2025 10:12:15</t>
+          <t>02-12-2025 07:32:30</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>05-12-2025 14:40:29</t>
+          <t>02-12-2025 09:33:22</t>
         </is>
       </c>
       <c r="J45" t="n">
-        <v>89787</v>
+        <v>14505</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -4009,75 +3998,80 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N45" t="n">
-        <v>76</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O45" t="n">
+        <v>40740</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>40740</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>16-03-2026 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>0</v>
+        <v>-0.3981770833333333</v>
       </c>
       <c r="T45" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>254535</v>
+        <v>255102</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>19</v>
+        <v>34.5</v>
       </c>
       <c r="E46" t="n">
-        <v>26.04166666666667</v>
+        <v>142.55</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>05-12-2025 14:40:29</t>
+          <t>02-12-2025 09:33:22</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>05-12-2025 14:59:29</t>
+          <t>02-12-2025 10:07:52</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>05-12-2025 14:59:29</t>
+          <t>02-12-2025 10:07:52</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>08-12-2025 07:25:31</t>
+          <t>02-12-2025 12:30:25</t>
         </is>
       </c>
       <c r="J46" t="n">
-        <v>3125</v>
+        <v>17106</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -4086,14 +4080,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N46" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -4103,11 +4097,11 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>14-11-2025 00:00:00</t>
+          <t>31-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>-31.47347222222222</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
         <v>2</v>
@@ -4115,46 +4109,46 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>254657</v>
+        <v>254856</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="E47" t="n">
-        <v>55.55833333333333</v>
+        <v>141.8416666666667</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>08-12-2025 07:25:31</t>
+          <t>02-12-2025 12:30:25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>08-12-2025 07:57:31</t>
+          <t>02-12-2025 13:02:55</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>08-12-2025 07:57:31</t>
+          <t>02-12-2025 13:02:55</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08-12-2025 08:53:05</t>
+          <t>03-12-2025 07:24:46</t>
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6667</v>
+        <v>17021</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -4167,11 +4161,14 @@
         </is>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N47" t="n">
         <v>70</v>
       </c>
+      <c r="O47" t="n">
+        <v>40684</v>
+      </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
@@ -4180,58 +4177,58 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>-24.53427662037037</v>
+        <v>-8</v>
       </c>
       <c r="T47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>254810</v>
+        <v>254597</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>04-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>19</v>
+        <v>44.5</v>
       </c>
       <c r="E48" t="n">
-        <v>144.675</v>
+        <v>91.85833333333333</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>08-12-2025 08:53:05</t>
+          <t>03-12-2025 07:24:46</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>08-12-2025 09:12:05</t>
+          <t>03-12-2025 08:09:16</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>08-12-2025 09:12:05</t>
+          <t>03-12-2025 08:09:16</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>08-12-2025 11:36:45</t>
+          <t>03-12-2025 09:41:07</t>
         </is>
       </c>
       <c r="J48" t="n">
-        <v>17361</v>
+        <v>11023</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -4240,11 +4237,11 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N48" t="n">
         <v>70</v>
@@ -4257,11 +4254,11 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>05-11-2025 00:00:00</t>
+          <t>10-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>-43.31460648148148</v>
+        <v>-3.403559027777778</v>
       </c>
       <c r="T48" t="n">
         <v>7</v>
@@ -4269,46 +4266,46 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>254268</v>
+        <v>254598</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>05-12-2025 14:00:00</t>
+          <t>04-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>17</v>
+        <v>30.5</v>
       </c>
       <c r="E49" t="n">
-        <v>51.6</v>
+        <v>104.2583333333333</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>08-12-2025 11:36:45</t>
+          <t>03-12-2025 09:41:07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>08-12-2025 11:53:45</t>
+          <t>03-12-2025 10:11:37</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>08-12-2025 11:53:45</t>
+          <t>03-12-2025 10:11:37</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>08-12-2025 12:45:21</t>
+          <t>03-12-2025 11:55:53</t>
         </is>
       </c>
       <c r="J49" t="n">
-        <v>6192</v>
+        <v>12511</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4317,11 +4314,11 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M49" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N49" t="n">
         <v>70</v>
@@ -4334,58 +4331,58 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>06-12-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>-12.36224537037037</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>254253</v>
+        <v>254603</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>CASON</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>05-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>17</v>
+        <v>30.5</v>
       </c>
       <c r="E50" t="n">
-        <v>181.1583333333333</v>
+        <v>91.85833333333333</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>08-12-2025 12:45:21</t>
+          <t>03-12-2025 11:55:53</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>08-12-2025 13:02:21</t>
+          <t>03-12-2025 12:26:23</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>08-12-2025 13:02:21</t>
+          <t>03-12-2025 12:26:23</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>09-12-2025 08:03:31</t>
+          <t>03-12-2025 13:58:14</t>
         </is>
       </c>
       <c r="J50" t="n">
-        <v>21739</v>
+        <v>11023</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4394,11 +4391,11 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>CASON ;H7</t>
         </is>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="N50" t="n">
         <v>70</v>
@@ -4411,19 +4408,19 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>10-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>-31.49985532407407</v>
+        <v>-3.582112268518518</v>
       </c>
       <c r="T50" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>254866</v>
+        <v>255338</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -4432,37 +4429,37 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>30-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>32.5</v>
+        <v>44.5</v>
       </c>
       <c r="E51" t="n">
-        <v>120.875</v>
+        <v>396.825</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>02-12-2025 07:00:00</t>
+          <t>03-12-2025 13:58:14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>02-12-2025 07:32:30</t>
+          <t>03-12-2025 14:42:44</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>02-12-2025 07:32:30</t>
+          <t>03-12-2025 14:42:44</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>02-12-2025 09:33:22</t>
+          <t>04-12-2025 13:19:34</t>
         </is>
       </c>
       <c r="J51" t="n">
-        <v>14505</v>
+        <v>47619</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4475,37 +4472,32 @@
         </is>
       </c>
       <c r="M51" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N51" t="n">
         <v>70</v>
       </c>
-      <c r="O51" t="n">
-        <v>40740</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P51" t="n">
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>40740</v>
+        <v>0</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>16-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>-0.3981770833333333</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>244023</v>
+        <v>254496</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -4514,37 +4506,37 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>17-09-2024 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D52" t="n">
         <v>32.5</v>
       </c>
       <c r="E52" t="n">
-        <v>8.308333333333334</v>
+        <v>53.50833333333333</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>02-12-2025 09:33:22</t>
+          <t>04-12-2025 13:19:34</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>02-12-2025 10:05:52</t>
+          <t>04-12-2025 13:52:04</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>02-12-2025 10:05:52</t>
+          <t>04-12-2025 13:52:04</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>02-12-2025 10:14:11</t>
+          <t>04-12-2025 14:45:34</t>
         </is>
       </c>
       <c r="J52" t="n">
-        <v>997</v>
+        <v>6421</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4557,7 +4549,7 @@
         </is>
       </c>
       <c r="M52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N52" t="n">
         <v>70</v>
@@ -4570,58 +4562,58 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>30-09-2024 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>-60</v>
+        <v>-30.61498263888889</v>
       </c>
       <c r="T52" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>254424</v>
+        <v>254575</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>28-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>36.5</v>
+        <v>65</v>
       </c>
       <c r="E53" t="n">
-        <v>10.95833333333333</v>
+        <v>49.43333333333333</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>02-12-2025 10:14:11</t>
+          <t>03-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>02-12-2025 10:50:41</t>
+          <t>03-12-2025 08:05:00</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>02-12-2025 10:50:41</t>
+          <t>03-12-2025 08:05:00</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>02-12-2025 11:01:38</t>
+          <t>03-12-2025 08:54:26</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>1315</v>
+        <v>5932</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4634,11 +4626,14 @@
         </is>
       </c>
       <c r="M53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
         <v>70</v>
       </c>
+      <c r="O53" t="n">
+        <v>40731</v>
+      </c>
       <c r="P53" t="n">
         <v>0</v>
       </c>
@@ -4647,58 +4642,58 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>24-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>-15.47882523148148</v>
+        <v>-10</v>
       </c>
       <c r="T53" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>254700</v>
+        <v>254196</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>27-11-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>34.5</v>
+        <v>25</v>
       </c>
       <c r="E54" t="n">
-        <v>91.72499999999999</v>
+        <v>153.4083333333333</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>02-12-2025 11:01:38</t>
+          <t>03-12-2025 08:54:26</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>02-12-2025 11:36:08</t>
+          <t>03-12-2025 09:19:26</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>02-12-2025 11:36:08</t>
+          <t>03-12-2025 09:19:26</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>02-12-2025 13:07:52</t>
+          <t>03-12-2025 11:52:50</t>
         </is>
       </c>
       <c r="J54" t="n">
-        <v>11007</v>
+        <v>18409</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4711,67 +4706,72 @@
         </is>
       </c>
       <c r="M54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
         <v>70</v>
       </c>
-      <c r="P54" t="n">
-        <v>0</v>
+      <c r="O54" t="n">
+        <v>40744</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>40744</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>19-12-2025 00:00:00</t>
+          <t>12-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>0</v>
+        <v>-0.4950289351851852</v>
       </c>
       <c r="T54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>254597</v>
+        <v>254602</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>50.5</v>
+        <v>70</v>
       </c>
       <c r="E55" t="n">
         <v>91.85833333333333</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>02-12-2025 13:07:52</t>
+          <t>03-12-2025 11:52:50</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>02-12-2025 13:58:22</t>
+          <t>03-12-2025 13:02:50</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>02-12-2025 13:58:22</t>
+          <t>03-12-2025 13:02:50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>03-12-2025 07:30:13</t>
+          <t>03-12-2025 14:34:42</t>
         </is>
       </c>
       <c r="J55" t="n">
@@ -4805,7 +4805,7 @@
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>-4.332008101851851</v>
+        <v>-3.607430555555556</v>
       </c>
       <c r="T55" t="n">
         <v>7</v>
@@ -4813,11 +4813,11 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>254938</v>
+        <v>255220</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4826,33 +4826,33 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>50.5</v>
+        <v>60</v>
       </c>
       <c r="E56" t="n">
-        <v>90.58333333333333</v>
+        <v>28.425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>03-12-2025 07:30:13</t>
+          <t>03-12-2025 14:34:42</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>03-12-2025 08:20:43</t>
+          <t>04-12-2025 07:34:42</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>03-12-2025 08:20:43</t>
+          <t>04-12-2025 07:34:42</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>03-12-2025 09:51:18</t>
+          <t>04-12-2025 08:03:07</t>
         </is>
       </c>
       <c r="J56" t="n">
-        <v>10870</v>
+        <v>3411</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4865,24 +4865,29 @@
         </is>
       </c>
       <c r="M56" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N56" t="n">
         <v>70</v>
       </c>
-      <c r="P56" t="n">
-        <v>0</v>
+      <c r="O56" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>09-12-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>-5.429982638888889</v>
+        <v>-0.3355034722222222</v>
       </c>
       <c r="T56" t="n">
         <v>2</v>
@@ -4890,11 +4895,11 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>254978</v>
+        <v>254820</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>H7</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4903,33 +4908,33 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>34.5</v>
+        <v>35</v>
       </c>
       <c r="E57" t="n">
-        <v>22.81666666666667</v>
+        <v>57.46666666666667</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>03-12-2025 09:51:18</t>
+          <t>04-12-2025 08:03:07</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>03-12-2025 10:25:48</t>
+          <t>04-12-2025 08:38:07</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>03-12-2025 10:25:48</t>
+          <t>04-12-2025 08:38:07</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>03-12-2025 10:48:37</t>
+          <t>04-12-2025 09:35:35</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>2738</v>
+        <v>6896</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4942,76 +4947,71 @@
         </is>
       </c>
       <c r="M57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N57" t="n">
         <v>70</v>
       </c>
-      <c r="O57" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P57" t="n">
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>28-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>-0.4697858796296296</v>
+        <v>-16.39971643518518</v>
       </c>
       <c r="T57" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>254255</v>
+        <v>255334</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CASON</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>32.5</v>
+        <v>17</v>
       </c>
       <c r="E58" t="n">
-        <v>43.45833333333334</v>
+        <v>153.9583333333333</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>03-12-2025 10:48:37</t>
+          <t>03-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>03-12-2025 11:21:07</t>
+          <t>03-12-2025 07:17:00</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>03-12-2025 11:21:07</t>
+          <t>03-12-2025 07:17:00</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>03-12-2025 12:04:35</t>
+          <t>03-12-2025 09:50:57</t>
         </is>
       </c>
       <c r="J58" t="n">
-        <v>5215</v>
+        <v>18475</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5020,14 +5020,14 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M58" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N58" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
@@ -5037,58 +5037,58 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>02-11-2025 00:00:00</t>
+          <t>07-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>-42.52253472222223</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>254196</v>
+        <v>254686</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="E59" t="n">
-        <v>153.4083333333333</v>
+        <v>53.66666666666666</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>03-12-2025 09:50:57</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>03-12-2025 08:05:00</t>
+          <t>03-12-2025 10:07:57</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>03-12-2025 08:05:00</t>
+          <t>03-12-2025 10:07:57</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>03-12-2025 10:38:24</t>
+          <t>03-12-2025 11:01:37</t>
         </is>
       </c>
       <c r="J59" t="n">
-        <v>18409</v>
+        <v>6440</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5097,80 +5097,78 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M59" t="n">
         <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O59" t="n">
-        <v>40744</v>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>40731</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>40744</v>
+        <v>0</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>12-11-2025 00:00:00</t>
+          <t>20-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>-0.4433391203703704</v>
+        <v>-14</v>
       </c>
       <c r="T59" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>255046</v>
+        <v>252692</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E60" t="n">
-        <v>47.65</v>
+        <v>35.24166666666667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>03-12-2025 10:38:24</t>
+          <t>03-12-2025 11:01:37</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>03-12-2025 11:08:24</t>
+          <t>03-12-2025 11:18:37</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>03-12-2025 11:08:24</t>
+          <t>03-12-2025 11:18:37</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>03-12-2025 11:56:03</t>
+          <t>03-12-2025 11:53:52</t>
         </is>
       </c>
       <c r="J60" t="n">
-        <v>5718</v>
+        <v>4229</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5179,80 +5177,75 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M60" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N60" t="n">
-        <v>70</v>
-      </c>
-      <c r="O60" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>40731</v>
+        <v>0</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>05-09-2025 00:00:00</t>
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="T60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>234538</v>
+        <v>255368</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>30-11-2025 14:00:00</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E61" t="n">
-        <v>77.075</v>
+        <v>475.45</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>03-12-2025 11:56:03</t>
+          <t>03-12-2025 11:53:52</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>03-12-2025 12:21:03</t>
+          <t>03-12-2025 12:14:52</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>03-12-2025 12:21:03</t>
+          <t>03-12-2025 12:14:52</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>03-12-2025 13:38:08</t>
+          <t>04-12-2025 12:10:19</t>
         </is>
       </c>
       <c r="J61" t="n">
-        <v>9249</v>
+        <v>57054</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5261,80 +5254,75 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M61" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N61" t="n">
-        <v>70</v>
-      </c>
-      <c r="O61" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>76</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>40731</v>
+        <v>0</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>15-01-2026 00:00:00</t>
         </is>
       </c>
       <c r="S61" s="1" t="n">
         <v>0</v>
       </c>
       <c r="T61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>255220</v>
+        <v>255046</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:00</t>
+          <t>02-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E62" t="n">
-        <v>28.425</v>
+        <v>47.65</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>03-12-2025 13:38:08</t>
+          <t>03-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>03-12-2025 14:18:08</t>
+          <t>03-12-2025 07:35:00</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>03-12-2025 14:18:08</t>
+          <t>03-12-2025 07:35:00</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>03-12-2025 14:46:33</t>
+          <t>03-12-2025 08:22:39</t>
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3411</v>
+        <v>5718</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5347,13 +5335,13 @@
         </is>
       </c>
       <c r="M62" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
         <v>70</v>
       </c>
       <c r="O62" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5361,11 +5349,11 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>40745</v>
+        <v>40731</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S62" s="1" t="n">
@@ -5377,11 +5365,11 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>254602</v>
+        <v>234538</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5390,33 +5378,33 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E63" t="n">
-        <v>91.85833333333333</v>
+        <v>77.075</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>03-12-2025 14:46:33</t>
+          <t>03-12-2025 08:22:39</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>04-12-2025 07:46:33</t>
+          <t>03-12-2025 08:47:39</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>04-12-2025 07:46:33</t>
+          <t>03-12-2025 08:47:39</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>04-12-2025 09:18:25</t>
+          <t>03-12-2025 10:04:43</t>
         </is>
       </c>
       <c r="J63" t="n">
-        <v>11023</v>
+        <v>9249</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5425,40 +5413,45 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M63" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
         <v>70</v>
       </c>
-      <c r="P63" t="n">
-        <v>0</v>
+      <c r="O63" t="n">
+        <v>40731</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>40731</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>10-12-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>-4.387789351851852</v>
+        <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>254603</v>
+        <v>255158</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5467,33 +5460,33 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E64" t="n">
-        <v>91.85833333333333</v>
+        <v>85.46666666666667</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>04-12-2025 09:18:25</t>
+          <t>03-12-2025 10:04:43</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>04-12-2025 09:43:25</t>
+          <t>03-12-2025 10:34:43</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>04-12-2025 09:43:25</t>
+          <t>03-12-2025 10:34:43</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>04-12-2025 11:15:16</t>
+          <t>03-12-2025 12:00:11</t>
         </is>
       </c>
       <c r="J64" t="n">
-        <v>11023</v>
+        <v>10256</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5502,15 +5495,18 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M64" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N64" t="n">
         <v>70</v>
       </c>
+      <c r="O64" t="n">
+        <v>40684</v>
+      </c>
       <c r="P64" t="n">
         <v>0</v>
       </c>
@@ -5519,11 +5515,11 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>10-12-2025 00:00:00</t>
+          <t>02-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>-4.468940972222223</v>
+        <v>-10</v>
       </c>
       <c r="T64" t="n">
         <v>7</v>
@@ -5531,46 +5527,46 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>254598</v>
+        <v>254812</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>H7</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>04-11-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E65" t="n">
-        <v>104.2583333333333</v>
+        <v>41.60833333333333</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>04-12-2025 11:15:16</t>
+          <t>03-12-2025 12:00:11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>04-12-2025 11:40:16</t>
+          <t>03-12-2025 12:35:11</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>04-12-2025 11:40:16</t>
+          <t>03-12-2025 12:35:11</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>04-12-2025 13:24:32</t>
+          <t>03-12-2025 13:16:48</t>
         </is>
       </c>
       <c r="J65" t="n">
-        <v>12511</v>
+        <v>4993</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5579,14 +5575,14 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CASON ;H7</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M65" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="P65" t="n">
         <v>0</v>
@@ -5596,11 +5592,11 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>15-12-2025 00:00:00</t>
+          <t>25-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>0</v>
+        <v>-18.58686342592593</v>
       </c>
       <c r="T65" t="n">
         <v>7</v>
@@ -5608,46 +5604,46 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>254686</v>
+        <v>254898</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="E66" t="n">
-        <v>53.66666666666666</v>
+        <v>30.96666666666667</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>03-12-2025 13:16:48</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>03-12-2025 07:19:00</t>
+          <t>03-12-2025 13:51:48</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>03-12-2025 07:19:00</t>
+          <t>03-12-2025 13:51:48</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>03-12-2025 08:12:40</t>
+          <t>03-12-2025 14:22:46</t>
         </is>
       </c>
       <c r="J66" t="n">
-        <v>6440</v>
+        <v>3716</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5656,78 +5652,80 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M66" t="n">
         <v>4</v>
       </c>
       <c r="N66" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="O66" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P66" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>20-11-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>-14</v>
+        <v>-0.2993402777777778</v>
       </c>
       <c r="T66" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>252692</v>
+        <v>254911</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E67" t="n">
-        <v>35.24166666666667</v>
+        <v>135.7</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>03-12-2025 08:12:40</t>
+          <t>03-12-2025 14:22:46</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>03-12-2025 08:29:40</t>
+          <t>03-12-2025 14:57:46</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>03-12-2025 08:29:40</t>
+          <t>03-12-2025 14:57:46</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>03-12-2025 09:04:54</t>
+          <t>04-12-2025 09:13:28</t>
         </is>
       </c>
       <c r="J67" t="n">
-        <v>4229</v>
+        <v>16284</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5736,28 +5734,33 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;H7 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>76</v>
-      </c>
-      <c r="P67" t="n">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="O67" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>05-09-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>-60</v>
+        <v>-0.4178819444444444</v>
       </c>
       <c r="T67" t="n">
         <v>1</v>
@@ -5765,46 +5768,46 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>255368</v>
+        <v>255027</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>R12</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>30-11-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E68" t="n">
-        <v>475.45</v>
+        <v>284.8</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>03-12-2025 09:04:54</t>
+          <t>04-12-2025 09:13:28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>03-12-2025 09:25:54</t>
+          <t>04-12-2025 09:38:28</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>03-12-2025 09:25:54</t>
+          <t>04-12-2025 09:38:28</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>04-12-2025 09:21:21</t>
+          <t>04-12-2025 14:23:16</t>
         </is>
       </c>
       <c r="J68" t="n">
-        <v>57054</v>
+        <v>34176</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5813,14 +5816,14 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M68" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="N68" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="P68" t="n">
         <v>0</v>
@@ -5830,19 +5833,19 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>15-01-2026 00:00:00</t>
+          <t>08-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>0</v>
+        <v>-7.2996875</v>
       </c>
       <c r="T68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>254592</v>
+        <v>255233</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -5851,37 +5854,37 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E69" t="n">
-        <v>59.86666666666667</v>
+        <v>92.41666666666667</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>03-12-2025 07:00:00</t>
+          <t>04-12-2025 14:23:16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>03-12-2025 07:30:00</t>
+          <t>04-12-2025 14:48:16</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>03-12-2025 07:30:00</t>
+          <t>04-12-2025 14:48:16</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>03-12-2025 08:29:52</t>
+          <t>05-12-2025 08:20:41</t>
         </is>
       </c>
       <c r="J69" t="n">
-        <v>7184</v>
+        <v>11090</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5899,71 +5902,66 @@
       <c r="N69" t="n">
         <v>70</v>
       </c>
-      <c r="O69" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P69" t="n">
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>0</v>
+        <v>-0.3812268518518518</v>
       </c>
       <c r="T69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>251289</v>
+        <v>255028</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E70" t="n">
-        <v>161.0333333333333</v>
+        <v>280.55</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>02-12-2025 07:00:00</t>
+          <t>05-12-2025 08:20:41</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>02-12-2025 07:35:00</t>
+          <t>05-12-2025 08:45:41</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>02-12-2025 07:35:00</t>
+          <t>05-12-2025 08:45:41</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>02-12-2025 10:16:02</t>
+          <t>05-12-2025 13:26:14</t>
         </is>
       </c>
       <c r="J70" t="n">
-        <v>19324</v>
+        <v>33666</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5972,18 +5970,15 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N70" t="n">
         <v>70</v>
       </c>
-      <c r="O70" t="n">
-        <v>40731</v>
-      </c>
       <c r="P70" t="n">
         <v>0</v>
       </c>
@@ -5992,58 +5987,58 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>01-12-2025 00:00:00</t>
+          <t>08-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>-3</v>
+        <v>-7.593414351851852</v>
       </c>
       <c r="T70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>255170</v>
+        <v>255063</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>05-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E71" t="n">
-        <v>8.333333333333334</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>02-12-2025 10:16:02</t>
+          <t>05-12-2025 13:26:14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>02-12-2025 10:51:02</t>
+          <t>05-12-2025 13:51:14</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>02-12-2025 10:51:02</t>
+          <t>05-12-2025 13:51:14</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>02-12-2025 10:59:22</t>
+          <t>08-12-2025 08:55:31</t>
         </is>
       </c>
       <c r="J71" t="n">
-        <v>1000</v>
+        <v>22114</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6052,80 +6047,75 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N71" t="n">
-        <v>76</v>
-      </c>
-      <c r="O71" t="n">
-        <v>40744</v>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>40744</v>
+        <v>0</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>30-11-2025 00:00:00</t>
+          <t>09-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>0</v>
+        <v>-9.405416666666667</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>254532</v>
+        <v>250049</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>01-12-2025 14:00:00</t>
+          <t>05-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D72" t="n">
         <v>30</v>
       </c>
       <c r="E72" t="n">
-        <v>83.34166666666667</v>
+        <v>104.1666666666667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>02-12-2025 10:59:22</t>
+          <t>08-12-2025 08:55:31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>02-12-2025 11:29:22</t>
+          <t>08-12-2025 09:25:31</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>02-12-2025 11:29:22</t>
+          <t>08-12-2025 09:25:31</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>02-12-2025 12:52:42</t>
+          <t>08-12-2025 11:09:41</t>
         </is>
       </c>
       <c r="J72" t="n">
-        <v>10001</v>
+        <v>12500</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6134,41 +6124,36 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M72" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" t="n">
+        <v>70</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>28-11-2025 00:00:00</t>
+        </is>
+      </c>
+      <c r="S72" s="1" t="n">
+        <v>-20.49858796296296</v>
+      </c>
+      <c r="T72" t="n">
         <v>4</v>
-      </c>
-      <c r="N72" t="n">
-        <v>76</v>
-      </c>
-      <c r="O72" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>40745</v>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>15-11-2025 00:00:00</t>
-        </is>
-      </c>
-      <c r="S72" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>254511</v>
+        <v>255221</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -6181,33 +6166,33 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E73" t="n">
-        <v>129.5916666666667</v>
+        <v>30.01666666666667</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>02-12-2025 12:52:42</t>
+          <t>02-12-2025 07:00:00</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>02-12-2025 13:22:42</t>
+          <t>02-12-2025 07:35:00</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>02-12-2025 13:22:42</t>
+          <t>02-12-2025 07:35:00</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>03-12-2025 07:32:18</t>
+          <t>02-12-2025 08:05:01</t>
         </is>
       </c>
       <c r="J73" t="n">
-        <v>15551</v>
+        <v>3602</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6220,32 +6205,37 @@
         </is>
       </c>
       <c r="M73" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N73" t="n">
         <v>76</v>
       </c>
-      <c r="P73" t="n">
-        <v>0</v>
+      <c r="O73" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>17-11-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>-26.31409722222222</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>255158</v>
+        <v>254540</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -6254,37 +6244,37 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>02-12-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>35</v>
       </c>
       <c r="E74" t="n">
-        <v>85.46666666666667</v>
+        <v>41.63333333333333</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>03-12-2025 07:32:18</t>
+          <t>02-12-2025 08:05:01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>03-12-2025 08:07:18</t>
+          <t>02-12-2025 08:40:01</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>03-12-2025 08:07:18</t>
+          <t>02-12-2025 08:40:01</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>03-12-2025 09:32:46</t>
+          <t>02-12-2025 09:21:39</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>10256</v>
+        <v>4996</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6293,31 +6283,33 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M74" t="n">
         <v>4</v>
       </c>
       <c r="N74" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O74" t="n">
-        <v>40684</v>
-      </c>
-      <c r="P74" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T74" t="n">
         <v>7</v>
@@ -6325,7 +6317,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>254575</v>
+        <v>254537</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -6334,37 +6326,37 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>28-11-2025 14:00:00</t>
+          <t>01-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E75" t="n">
-        <v>49.43333333333333</v>
+        <v>41.63333333333333</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>03-12-2025 09:32:46</t>
+          <t>02-12-2025 09:21:39</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>03-12-2025 10:12:46</t>
+          <t>02-12-2025 09:46:39</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>03-12-2025 10:12:46</t>
+          <t>02-12-2025 09:46:39</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>03-12-2025 11:02:12</t>
+          <t>02-12-2025 10:28:17</t>
         </is>
       </c>
       <c r="J75" t="n">
-        <v>5932</v>
+        <v>4996</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6373,31 +6365,33 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M75" t="n">
         <v>4</v>
       </c>
       <c r="N75" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O75" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
+        <v>40745</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>24-11-2025 00:00:00</t>
+          <t>15-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
         <v>7</v>
@@ -6405,7 +6399,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>254531</v>
+        <v>254364</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -6418,33 +6412,33 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E76" t="n">
-        <v>44.15</v>
+        <v>26.48333333333333</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>03-12-2025 11:02:12</t>
+          <t>02-12-2025 10:28:17</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>03-12-2025 11:47:12</t>
+          <t>02-12-2025 11:03:17</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>03-12-2025 11:47:12</t>
+          <t>02-12-2025 11:03:17</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>03-12-2025 12:31:21</t>
+          <t>02-12-2025 11:29:46</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5298</v>
+        <v>3178</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6453,41 +6447,36 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;R12 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N76" t="n">
-        <v>76</v>
-      </c>
-      <c r="O76" t="n">
-        <v>40745</v>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+        <v>70</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>40745</v>
+        <v>0</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>15-11-2025 00:00:00</t>
+          <t>14-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>0</v>
+        <v>-29.60686342592593</v>
       </c>
       <c r="T76" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>254915</v>
+        <v>254582</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -6496,37 +6485,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>30-11-2025 14:00:00</t>
+          <t>03-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E77" t="n">
-        <v>48.875</v>
+        <v>46.675</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>03-12-2025 12:31:21</t>
+          <t>02-12-2025 11:29:46</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>03-12-2025 13:11:21</t>
+          <t>02-12-2025 12:04:46</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>03-12-2025 13:11:21</t>
+          <t>02-12-2025 12:04:46</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:13</t>
+          <t>02-12-2025 12:51:26</t>
         </is>
       </c>
       <c r="J77" t="n">
-        <v>5865</v>
+        <v>5601</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6535,36 +6524,41 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N77" t="n">
         <v>70</v>
       </c>
-      <c r="P77" t="n">
-        <v>0</v>
+      <c r="O77" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>12-01-2026 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>0</v>
+        <v>-0.3302488425925926</v>
       </c>
       <c r="T77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>254911</v>
+        <v>254585</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -6577,33 +6571,33 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E78" t="n">
-        <v>135.7</v>
+        <v>46.675</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>03-12-2025 14:00:13</t>
+          <t>02-12-2025 12:51:26</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>03-12-2025 14:30:13</t>
+          <t>02-12-2025 13:16:26</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>03-12-2025 14:30:13</t>
+          <t>02-12-2025 13:16:26</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>04-12-2025 08:45:55</t>
+          <t>02-12-2025 14:03:07</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>16284</v>
+        <v>5601</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6612,11 +6606,11 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N78" t="n">
         <v>70</v>
@@ -6634,11 +6628,11 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>01-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>-0.3652256944444445</v>
+        <v>-0.3800231481481481</v>
       </c>
       <c r="T78" t="n">
         <v>1</v>
@@ -6646,7 +6640,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>254551</v>
+        <v>254881</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -6659,33 +6653,33 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E79" t="n">
-        <v>189.8666666666667</v>
+        <v>144.675</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>04-12-2025 08:45:55</t>
+          <t>02-12-2025 14:03:07</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>04-12-2025 09:10:55</t>
+          <t>02-12-2025 14:33:07</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>04-12-2025 09:10:55</t>
+          <t>02-12-2025 14:33:07</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>04-12-2025 12:20:47</t>
+          <t>03-12-2025 08:57:47</t>
         </is>
       </c>
       <c r="J79" t="n">
-        <v>22784</v>
+        <v>17361</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6694,41 +6688,36 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
         <v>70</v>
       </c>
-      <c r="O79" t="n">
-        <v>40731</v>
-      </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
+      <c r="P79" t="n">
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>40731</v>
+        <v>0</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>-0.5144386574074075</v>
+        <v>-10.50132523148148</v>
       </c>
       <c r="T79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>255027</v>
+        <v>254258</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -6744,30 +6733,30 @@
         <v>25</v>
       </c>
       <c r="E80" t="n">
-        <v>284.8</v>
+        <v>144.675</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>04-12-2025 12:20:47</t>
+          <t>03-12-2025 08:57:47</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>04-12-2025 12:45:47</t>
+          <t>03-12-2025 09:22:47</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>04-12-2025 12:45:47</t>
+          <t>03-12-2025 09:22:47</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>05-12-2025 09:30:35</t>
+          <t>03-12-2025 11:47:28</t>
         </is>
       </c>
       <c r="J80" t="n">
-        <v>34176</v>
+        <v>17361</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6776,11 +6765,11 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
         </is>
       </c>
       <c r="M80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N80" t="n">
         <v>70</v>
@@ -6793,19 +6782,19 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>08-12-2025 00:00:00</t>
+          <t>04-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>-7.396244212962963</v>
+        <v>-10.61915509259259</v>
       </c>
       <c r="T80" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>253862</v>
+        <v>254708</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -6818,33 +6807,33 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E81" t="n">
-        <v>59.59166666666667</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>05-12-2025 09:30:35</t>
+          <t>03-12-2025 11:47:28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>05-12-2025 10:00:35</t>
+          <t>03-12-2025 12:22:28</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>05-12-2025 10:00:35</t>
+          <t>03-12-2025 12:22:28</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>05-12-2025 11:00:11</t>
+          <t>03-12-2025 13:30:19</t>
         </is>
       </c>
       <c r="J81" t="n">
-        <v>7151</v>
+        <v>8142</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6853,28 +6842,33 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;H7 ;R5 ;R9</t>
+          <t>BIMEC 3 ;BIMEC 4 ;BIMEC 5 ;CASON ;R5 ;R9</t>
         </is>
       </c>
       <c r="M81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N81" t="n">
         <v>70</v>
       </c>
-      <c r="P81" t="n">
-        <v>0</v>
+      <c r="O81" t="n">
+        <v>40745</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>40745</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>05-12-2025 00:00:00</t>
+          <t>09-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>-10.45846064814815</v>
+        <v>-1.35724537037037</v>
       </c>
       <c r="T81" t="n">
         <v>1</v>
@@ -6882,7 +6876,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>254654</v>
+        <v>253862</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -6898,30 +6892,30 @@
         <v>30</v>
       </c>
       <c r="E82" t="n">
-        <v>80.51666666666667</v>
+        <v>59.59166666666667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>05-12-2025 11:00:11</t>
+          <t>03-12-2025 13:30:19</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>05-12-2025 11:30:11</t>
+          <t>03-12-2025 14:00:19</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>05-12-2025 11:30:11</t>
+          <t>03-12-2025 14:00:19</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>05-12-2025 12:50:42</t>
+          <t>03-12-2025 14:59:54</t>
         </is>
       </c>
       <c r="J82" t="n">
-        <v>9662</v>
+        <v>7151</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6934,7 +6928,7 @@
         </is>
       </c>
       <c r="M82" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N82" t="n">
         <v>70</v>
@@ -6947,19 +6941,19 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>21-11-2025 00:00:00</t>
+          <t>05-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>-24.53520833333333</v>
+        <v>-10.41946180555555</v>
       </c>
       <c r="T82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>254548</v>
+        <v>254657</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -6972,33 +6966,33 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E83" t="n">
-        <v>24.04166666666667</v>
+        <v>55.55833333333333</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>05-12-2025 12:50:42</t>
+          <t>03-12-2025 14:59:54</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>05-12-2025 13:30:42</t>
+          <t>04-12-2025 07:34:54</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>05-12-2025 13:30:42</t>
+          <t>04-12-2025 07:34:54</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>05-12-2025 13:54:44</t>
+          <t>04-12-2025 08:30:28</t>
         </is>
       </c>
       <c r="J83" t="n">
-        <v>2885</v>
+        <v>6667</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7011,7 +7005,7 @@
         </is>
       </c>
       <c r="M83" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="N83" t="n">
         <v>70</v>
@@ -7024,19 +7018,19 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>19-11-2025 00:00:00</t>
+          <t>21-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>-26.57968171296296</v>
+        <v>-24.48234953703704</v>
       </c>
       <c r="T83" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>254269</v>
+        <v>254810</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -7045,37 +7039,37 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>05-12-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E84" t="n">
-        <v>47.275</v>
+        <v>144.675</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>05-12-2025 13:54:44</t>
+          <t>04-12-2025 08:30:28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>05-12-2025 14:34:44</t>
+          <t>04-12-2025 09:05:28</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>05-12-2025 14:34:44</t>
+          <t>04-12-2025 09:05:28</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>08-12-2025 07:22:01</t>
+          <t>04-12-2025 11:30:08</t>
         </is>
       </c>
       <c r="J84" t="n">
-        <v>5673</v>
+        <v>17361</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7088,7 +7082,7 @@
         </is>
       </c>
       <c r="M84" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N84" t="n">
         <v>70</v>
@@ -7101,19 +7095,19 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>06-12-2025 00:00:00</t>
+          <t>05-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S84" s="1" t="n">
-        <v>-12.30695601851852</v>
+        <v>-40.60712384259259</v>
       </c>
       <c r="T84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>255084</v>
+        <v>254268</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -7129,30 +7123,30 @@
         <v>30</v>
       </c>
       <c r="E85" t="n">
-        <v>47.65</v>
+        <v>51.6</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>08-12-2025 07:22:01</t>
+          <t>04-12-2025 11:30:08</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>08-12-2025 07:52:01</t>
+          <t>04-12-2025 12:00:08</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>08-12-2025 07:52:01</t>
+          <t>04-12-2025 12:00:08</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>08-12-2025 08:39:40</t>
+          <t>04-12-2025 12:51:44</t>
         </is>
       </c>
       <c r="J85" t="n">
-        <v>5718</v>
+        <v>6192</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7165,7 +7159,7 @@
         </is>
       </c>
       <c r="M85" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N85" t="n">
         <v>70</v>
@@ -7178,19 +7172,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>10-12-2025 00:00:00</t>
+          <t>06-12-2025 00:00:00</t>
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>-8.360879629629629</v>
+        <v>-12.33045717592593</v>
       </c>
       <c r="T85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>250049</v>
+        <v>254253</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -7203,33 +7197,33 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E86" t="n">
-        <v>104.1666666666667</v>
+        <v>181.1583333333333</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>08-12-2025 08:39:40</t>
+          <t>04-12-2025 12:51:44</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>08-12-2025 09:14:40</t>
+          <t>04-12-2025 13:21:44</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>08-12-2025 09:14:40</t>
+          <t>04-12-2025 13:21:44</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>08-12-2025 10:58:50</t>
+          <t>05-12-2025 08:22:54</t>
         </is>
       </c>
       <c r="J86" t="n">
-        <v>12500</v>
+        <v>21739</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7255,19 +7249,19 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>28-11-2025 00:00:00</t>
+          <t>17-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>-20.45752314814815</v>
+        <v>-31.47709490740741</v>
       </c>
       <c r="T86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>254167</v>
+        <v>254548</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -7276,37 +7270,37 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>05-12-2025 14:00:00</t>
+          <t>04-12-2025 14:00:00</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E87" t="n">
-        <v>152.125</v>
+        <v>24.04166666666667</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>08-12-2025 10:58:50</t>
+          <t>05-12-2025 08:22:54</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>08-12-2025 11:33:50</t>
+          <t>05-12-2025 09:07:54</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>08-12-2025 11:33:50</t>
+          <t>05-12-2025 09:07:54</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>08-12-2025 14:05:57</t>
+          <t>05-12-2025 09:31:56</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>18255</v>
+        <v>2885</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7319,7 +7313,7 @@
         </is>
       </c>
       <c r="M87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="N87" t="n">
         <v>70</v>
@@ -7332,11 +7326,11 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>02-12-2025 00:00:00</t>
+          <t>19-11-2025 00:00:00</t>
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>-16.58747106481481</v>
+        <v>-29.52504050925926</v>
       </c>
       <c r="T87" t="n">
         <v>7</v>
@@ -7507,7 +7501,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BIMEC 5</t>
+          <t>BIMEC 3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7516,7 +7510,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E90" t="n">
         <v>154.975</v>
@@ -7528,17 +7522,17 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>10-12-2025 14:17:00</t>
+          <t>10-12-2025 14:19:00</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>10-12-2025 14:17:00</t>
+          <t>10-12-2025 14:19:00</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>11-12-2025 08:51:58</t>
+          <t>11-12-2025 08:53:58</t>
         </is>
       </c>
       <c r="J90" t="n">
@@ -7572,7 +7566,7 @@
         </is>
       </c>
       <c r="S90" s="1" t="n">
-        <v>-18.36942708333333</v>
+        <v>-18.37081597222222</v>
       </c>
       <c r="T90" t="n">
         <v>1</v>
